--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01394FC-EC8B-D24D-9664-0BA6B254163B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F079566-6141-824D-9ACC-DCB9C4B38316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26200" yWindow="600" windowWidth="25000" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1160" yWindow="600" windowWidth="50040" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -20,11 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="56">
   <si>
     <t>ActionId</t>
   </si>
   <si>
+    <t>ActionName</t>
+  </si>
+  <si>
     <t>GifPath</t>
   </si>
   <si>
@@ -43,123 +46,155 @@
     <t>资源备注，仅用于说明素材来源或用途</t>
   </si>
   <si>
-    <r>
-      <t>/ActionsGIF/180</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>甩尾</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.gif</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>Khezu_Check_Bite</t>
+  </si>
+  <si>
+    <t>牵制咬</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/牵制咬.gif</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Khezu_Back_Step</t>
+  </si>
+  <si>
+    <t>后撤步</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/正面后撤步.gif</t>
+  </si>
+  <si>
+    <t>Khezu_Dash_Bite</t>
+  </si>
+  <si>
+    <t>前冲咬</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/前冲咬.gif</t>
   </si>
   <si>
     <t>Khezu_Tail_Sweep</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionName</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>甩尾</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>/ActionsGIF/180甩尾.gif</t>
+  </si>
+  <si>
+    <t>Khezu_Tail_Thrust</t>
+  </si>
+  <si>
+    <t>尾刺-尾充能</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/尾巴插地放电-未充能.gif</t>
+  </si>
+  <si>
+    <t>Khezu_Tail_Ground_Spike_Uncharged</t>
+  </si>
+  <si>
+    <t>尾巴插地放电-未充能</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/充能尾刺.gif</t>
+  </si>
+  <si>
+    <t>Khezu_Head_Slam_Uncharged</t>
+  </si>
+  <si>
+    <t>头顶二连-未充能</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/头顶二连-未充能.gif</t>
+  </si>
+  <si>
+    <t>Khezu_Head_Slam_Charged</t>
+  </si>
+  <si>
+    <t>头顶二连-头充能</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/头顶二连-充能.gif</t>
+  </si>
+  <si>
+    <t>Khezu_Wing_Press_Uncharged</t>
+  </si>
+  <si>
+    <t>翅膀单次下拍-未充能</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/翅膀单次下拍-未充能.gif</t>
+  </si>
+  <si>
+    <t>Khezu_Wing_Double_Press_Charged</t>
+  </si>
+  <si>
+    <t>翅膀下拍二连-翅膀充能</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/翅膀二连拍-充能.gif</t>
+  </si>
+  <si>
+    <t>Khezu_Dash_Wing_Press_Charged</t>
+  </si>
+  <si>
+    <t>冲刺翅膀下拍-翅膀充能</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/冲刺翅膀下拍-充能.gif</t>
+  </si>
+  <si>
+    <t>Khezu_Double</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/</t>
+  </si>
+  <si>
+    <t>Khezu_Double_Breath_Charged</t>
+  </si>
+  <si>
+    <t>二连吐息-头、翅膀充能</t>
+  </si>
+  <si>
+    <t>Khezu_Overhead_Slam_Charged</t>
+  </si>
+  <si>
+    <t>斩舰刀-头充能</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/斩舰刀-充能.gif</t>
+  </si>
+  <si>
+    <t>Khezu_AllCharged_Roar</t>
+  </si>
+  <si>
+    <t>全身充能吼叫</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/进入完全充电状态.gif</t>
   </si>
   <si>
     <t>Khezu_</t>
   </si>
   <si>
-    <t>Khezu_CheckBite</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>/ActionsGIF/</t>
-  </si>
-  <si>
-    <r>
-      <t>/ActionsGIF/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F2937"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>牵制咬</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F2937"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>.gif</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>牵制咬</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Khezu_BackStep</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Khezu_Tail_Thrust</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>尾巴突刺</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>/ActionsGIF/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>充能尾刺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.gif</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>Khezu_Ult_Lightning_Dive</t>
+  </si>
+  <si>
+    <t>大招-闪电俯冲</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/大招-闪电俯冲.gif</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
@@ -188,26 +223,6 @@
       <sz val="9"/>
       <name val="FangSong"/>
       <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111827"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F2937"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F2937"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -276,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -291,14 +306,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -635,12 +642,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" customWidth="1"/>
+    <col min="3" max="3" width="47.6640625" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -649,242 +656,410 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A4" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.15">
-      <c r="A5" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="D5" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>11</v>
+      <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.15">
+      <c r="A8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>10</v>
+        <v>27</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>13</v>
+      <c r="A10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A11" t="s">
-        <v>11</v>
+      <c r="A11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>13</v>
+        <v>35</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>13</v>
+      <c r="A12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
-        <v>11</v>
+      <c r="A13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>13</v>
+        <v>41</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>13</v>
+      <c r="A14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A15" t="s">
-        <v>11</v>
+      <c r="A15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>13</v>
+        <v>43</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.15">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="5"/>
+      <c r="A16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="C17" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.15">
-      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.15">
-      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.15">
-      <c r="A22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.15">
-      <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15" x14ac:dyDescent="0.15">
-      <c r="A24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.15">
-      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A24" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15" x14ac:dyDescent="0.15">
-      <c r="A26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>13</v>
+        <v>43</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A28" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:D29" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F079566-6141-824D-9ACC-DCB9C4B38316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD135F0A-6CCC-4249-B876-532FF55EE9D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="600" windowWidth="50040" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12120" yWindow="4360" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
   <si>
     <t>ActionId</t>
   </si>
@@ -148,9 +148,6 @@
     <t>/ActionsGIF/冲刺翅膀下拍-充能.gif</t>
   </si>
   <si>
-    <t>Khezu_Double</t>
-  </si>
-  <si>
     <t>/ActionsGIF/</t>
   </si>
   <si>
@@ -188,13 +185,57 @@
   </si>
   <si>
     <t>/ActionsGIF/大招-闪电俯冲.gif</t>
+  </si>
+  <si>
+    <r>
+      <t>/ActionsGIF/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二连吐息</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头、翅膀充能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.gif</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
@@ -223,6 +264,13 @@
       <sz val="9"/>
       <name val="FangSong"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -642,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -833,232 +881,218 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.15">
+      <c r="A14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A15" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A17" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A18" s="5" t="s">
+      <c r="B18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A19" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A20" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A26" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A28" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A20" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A21" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A22" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A23" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A24" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A25" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A26" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A27" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A28" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A29" s="4" t="s">
+      <c r="B28" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="C28" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D29" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:D28" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD135F0A-6CCC-4249-B876-532FF55EE9D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24500BC4-E7D2-AB4D-B1C3-ABACDD125B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12120" yWindow="4360" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,9 +52,6 @@
     <t>牵制咬</t>
   </si>
   <si>
-    <t>/ActionsGIF/牵制咬.gif</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -64,90 +61,60 @@
     <t>后撤步</t>
   </si>
   <si>
-    <t>/ActionsGIF/正面后撤步.gif</t>
-  </si>
-  <si>
     <t>Khezu_Dash_Bite</t>
   </si>
   <si>
     <t>前冲咬</t>
   </si>
   <si>
-    <t>/ActionsGIF/前冲咬.gif</t>
-  </si>
-  <si>
     <t>Khezu_Tail_Sweep</t>
   </si>
   <si>
     <t>甩尾</t>
   </si>
   <si>
-    <t>/ActionsGIF/180甩尾.gif</t>
-  </si>
-  <si>
     <t>Khezu_Tail_Thrust</t>
   </si>
   <si>
     <t>尾刺-尾充能</t>
   </si>
   <si>
-    <t>/ActionsGIF/尾巴插地放电-未充能.gif</t>
-  </si>
-  <si>
     <t>Khezu_Tail_Ground_Spike_Uncharged</t>
   </si>
   <si>
     <t>尾巴插地放电-未充能</t>
   </si>
   <si>
-    <t>/ActionsGIF/充能尾刺.gif</t>
-  </si>
-  <si>
     <t>Khezu_Head_Slam_Uncharged</t>
   </si>
   <si>
     <t>头顶二连-未充能</t>
   </si>
   <si>
-    <t>/ActionsGIF/头顶二连-未充能.gif</t>
-  </si>
-  <si>
     <t>Khezu_Head_Slam_Charged</t>
   </si>
   <si>
     <t>头顶二连-头充能</t>
   </si>
   <si>
-    <t>/ActionsGIF/头顶二连-充能.gif</t>
-  </si>
-  <si>
     <t>Khezu_Wing_Press_Uncharged</t>
   </si>
   <si>
     <t>翅膀单次下拍-未充能</t>
   </si>
   <si>
-    <t>/ActionsGIF/翅膀单次下拍-未充能.gif</t>
-  </si>
-  <si>
     <t>Khezu_Wing_Double_Press_Charged</t>
   </si>
   <si>
     <t>翅膀下拍二连-翅膀充能</t>
   </si>
   <si>
-    <t>/ActionsGIF/翅膀二连拍-充能.gif</t>
-  </si>
-  <si>
     <t>Khezu_Dash_Wing_Press_Charged</t>
   </si>
   <si>
     <t>冲刺翅膀下拍-翅膀充能</t>
   </si>
   <si>
-    <t>/ActionsGIF/冲刺翅膀下拍-充能.gif</t>
-  </si>
-  <si>
     <t>/ActionsGIF/</t>
   </si>
   <si>
@@ -163,18 +130,12 @@
     <t>斩舰刀-头充能</t>
   </si>
   <si>
-    <t>/ActionsGIF/斩舰刀-充能.gif</t>
-  </si>
-  <si>
     <t>Khezu_AllCharged_Roar</t>
   </si>
   <si>
     <t>全身充能吼叫</t>
   </si>
   <si>
-    <t>/ActionsGIF/进入完全充电状态.gif</t>
-  </si>
-  <si>
     <t>Khezu_</t>
   </si>
   <si>
@@ -184,7 +145,46 @@
     <t>大招-闪电俯冲</t>
   </si>
   <si>
-    <t>/ActionsGIF/大招-闪电俯冲.gif</t>
+    <t>/ActionsGIF/技能/牵制咬.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/正面后撤步.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/前冲咬.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/180甩尾.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/尾巴插地放电-未充能.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/充能尾刺.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/头顶二连-未充能.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/头顶二连-充能.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/翅膀单次下拍-未充能.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/翅膀二连拍-充能.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/冲刺翅膀下拍-充能.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/二连吐息-头、翅膀充能.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/斩舰刀-充能.gif</t>
+  </si>
+  <si>
+    <t>/ActionsGIF/技能/进入完全充电状态.gif</t>
   </si>
   <si>
     <r>
@@ -198,7 +198,26 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>二连吐息</t>
+      <t>技能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大招</t>
     </r>
     <r>
       <rPr>
@@ -217,7 +236,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>头、翅膀充能</t>
+      <t>闪电俯冲</t>
     </r>
     <r>
       <rPr>
@@ -235,7 +254,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
@@ -272,6 +291,12 @@
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -339,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -356,6 +381,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -734,361 +760,361 @@
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
+      <c r="C3" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>14</v>
+      <c r="C4" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>35</v>
+        <v>26</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>38</v>
+        <v>28</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>41</v>
+        <v>30</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>47</v>
+        <v>35</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>50</v>
+        <v>37</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24500BC4-E7D2-AB4D-B1C3-ABACDD125B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BECD618-BC00-834C-AA90-DFEE495F62D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12120" yWindow="4360" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="59">
   <si>
     <t>ActionId</t>
   </si>
@@ -242,6 +242,105 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.gif</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Khezu_Breath_Uncharged</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吐息</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>未充能</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>/ActionsGIF/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电流吐息</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>未充能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -254,7 +353,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
@@ -297,6 +396,20 @@
       <color rgb="FF333333"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="7">
@@ -364,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -382,6 +495,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -716,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -907,219 +1023,232 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A15" s="5" t="s">
+      <c r="D15" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A16" s="4" t="s">
+      <c r="D16" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A17" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A17" s="5" t="s">
+      <c r="D17" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A18" s="4" t="s">
+      <c r="D18" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="B19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A19" s="5" t="s">
+      <c r="D19" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="B20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A20" s="4" t="s">
+      <c r="D20" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A21" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="B21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A21" s="5" t="s">
+      <c r="D21" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A22" s="4" t="s">
+      <c r="D22" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A23" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="B23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A23" s="5" t="s">
+      <c r="D23" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A24" s="4" t="s">
+      <c r="D24" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A25" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="B25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A25" s="5" t="s">
+      <c r="D25" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A26" s="4" t="s">
+      <c r="D26" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A27" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="4" t="s">
+      <c r="B27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A27" s="5" t="s">
+      <c r="D27" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="18" x14ac:dyDescent="0.15">
-      <c r="A28" s="4" t="s">
+      <c r="D28" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.15">
+      <c r="A29" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C29" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D28" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:D29" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BECD618-BC00-834C-AA90-DFEE495F62D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B94E074-7141-2A4E-B16A-352C45EDDCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12120" yWindow="4360" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -933,10 +933,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.15">
@@ -947,7 +947,7 @@
         <v>20</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>

--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B94E074-7141-2A4E-B16A-352C45EDDCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9584DE96-688D-054B-909A-DF73A1FBC8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12120" yWindow="4360" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10820" yWindow="7260" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="62">
   <si>
     <t>ActionId</t>
   </si>
@@ -346,6 +346,38 @@
       </rPr>
       <t>.gif</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>/ActionsGIF/Combo/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小咬甩尾尾刺三连</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.gif</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>小咬甩尾尾刺三连</t>
+  </si>
+  <si>
+    <t>Khezu_Head_Tail_Combo</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1077,15 +1109,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" ht="18" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
+        <v>61</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>10</v>

--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9584DE96-688D-054B-909A-DF73A1FBC8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7B2CF0-460E-064E-B926-50875E89F017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10820" yWindow="7260" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12560" yWindow="10520" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
   <si>
     <t>ActionId</t>
   </si>
@@ -55,9 +55,6 @@
     <t/>
   </si>
   <si>
-    <t>Khezu_Back_Step</t>
-  </si>
-  <si>
     <t>后撤步</t>
   </si>
   <si>
@@ -109,16 +106,10 @@
     <t>翅膀下拍二连-翅膀充能</t>
   </si>
   <si>
-    <t>Khezu_Dash_Wing_Press_Charged</t>
-  </si>
-  <si>
     <t>冲刺翅膀下拍-翅膀充能</t>
   </si>
   <si>
     <t>/ActionsGIF/</t>
-  </si>
-  <si>
-    <t>Khezu_Double_Breath_Charged</t>
   </si>
   <si>
     <t>二连吐息-头、翅膀充能</t>
@@ -374,10 +365,48 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>Khezu_Head_Tail_Combo</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Khezu_Double_Breath_Charged</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Khezu_Back_Step</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Khezu_Dash_Wing_Press_Charged</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>小咬甩尾尾刺三连</t>
-  </si>
-  <si>
-    <t>Khezu_Head_Tail_Combo</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>/ActionsGIF/Combo/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二连吐息+冲刺翅膀拍-头翅膀充电</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.gif</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -385,7 +414,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
@@ -440,6 +469,13 @@
       <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -509,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -528,6 +564,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -865,7 +904,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" customWidth="1"/>
@@ -873,7 +912,7 @@
     <col min="4" max="4" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="26" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -887,7 +926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="42" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -901,7 +940,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" ht="15">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -909,369 +948,369 @@
         <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15">
+      <c r="A4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15">
+      <c r="A6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="D6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="6" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="15">
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15">
+      <c r="A9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="D9" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15">
+      <c r="A10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15">
+      <c r="A11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="D11" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15">
+      <c r="A12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="D12" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15">
+      <c r="A13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="D13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18">
+      <c r="A14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="15">
+      <c r="A15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="D15" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15">
+      <c r="A16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A13" s="4" t="s">
+      <c r="D16" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15">
+      <c r="A17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18">
+      <c r="A18" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18">
+      <c r="A19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15">
+      <c r="A20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="D20" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15">
+      <c r="A21" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15">
+      <c r="A22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15">
+      <c r="A23" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15">
+      <c r="A24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15">
+      <c r="A25" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15">
+      <c r="A26" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15">
+      <c r="A27" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15">
+      <c r="A28" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18">
+      <c r="A29" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="18" x14ac:dyDescent="0.15">
-      <c r="A18" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A19" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A21" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A23" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A25" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A27" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.15">
-      <c r="A29" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>10</v>

--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7B2CF0-460E-064E-B926-50875E89F017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C69916D-7678-0442-B755-5290FB9D0A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12560" yWindow="10520" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1160" yWindow="600" windowWidth="50040" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="68">
   <si>
     <t>ActionId</t>
   </si>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>甩尾</t>
-  </si>
-  <si>
-    <t>Khezu_Tail_Thrust</t>
   </si>
   <si>
     <t>尾刺-尾充能</t>
@@ -408,13 +405,48 @@
       <t>.gif</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Khezu_Tail_Thrust</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>/ActionsGIF/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技能/二连甩头.gif</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Khezu_Head_Double_Swing_Charged</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>二连甩头-头、翅膀充能</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Khezu_Double_Breath_Combo</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>二连吐息+冲刺翅膀拍-头翅膀充电</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
@@ -475,6 +507,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF111827"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -545,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -567,6 +606,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -903,12 +945,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" customWidth="1"/>
-    <col min="3" max="3" width="47.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" customWidth="1"/>
+    <col min="3" max="3" width="48.6640625" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -948,7 +990,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>10</v>
@@ -956,13 +998,13 @@
     </row>
     <row r="4" spans="1:4" ht="15">
       <c r="A4" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -976,7 +1018,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>10</v>
@@ -990,7 +1032,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -998,27 +1040,27 @@
     </row>
     <row r="7" spans="1:4" ht="15">
       <c r="A7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="C7" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15">
       <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="C8" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -1026,13 +1068,13 @@
     </row>
     <row r="9" spans="1:4" ht="15">
       <c r="A9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="C9" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>10</v>
@@ -1040,13 +1082,13 @@
     </row>
     <row r="10" spans="1:4" ht="15">
       <c r="A10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="C10" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -1054,13 +1096,13 @@
     </row>
     <row r="11" spans="1:4" ht="15">
       <c r="A11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="C11" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>10</v>
@@ -1068,13 +1110,13 @@
     </row>
     <row r="12" spans="1:4" ht="15">
       <c r="A12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="C12" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>10</v>
@@ -1082,13 +1124,13 @@
     </row>
     <row r="13" spans="1:4" ht="15">
       <c r="A13" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>10</v>
@@ -1096,228 +1138,240 @@
     </row>
     <row r="14" spans="1:4" ht="18">
       <c r="A14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="15">
       <c r="A15" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18">
+      <c r="A16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="15">
+      <c r="A17" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15">
-      <c r="A16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="D17" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15">
+      <c r="A18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="B18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15">
-      <c r="A17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="D18" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18">
+      <c r="A19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18">
+      <c r="A20" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15">
+      <c r="A21" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15">
+      <c r="A22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15">
+      <c r="A23" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15">
+      <c r="A24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15">
+      <c r="A25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15">
+      <c r="A26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15">
+      <c r="A27" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15">
+      <c r="A28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15">
+      <c r="A29" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18">
+      <c r="A30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="18">
-      <c r="A18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="18">
-      <c r="A19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15">
-      <c r="A20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15">
-      <c r="A21" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15">
-      <c r="A22" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15">
-      <c r="A23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15">
-      <c r="A24" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15">
-      <c r="A25" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15">
-      <c r="A26" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15">
-      <c r="A27" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15">
-      <c r="A28" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="18">
-      <c r="A29" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D29" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:D30" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C69916D-7678-0442-B755-5290FB9D0A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAC567A-CA4C-7544-B367-56FF96A457D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="600" windowWidth="50040" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6140" yWindow="4100" windowWidth="44820" windowHeight="25320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -133,9 +133,6 @@
     <t>大招-闪电俯冲</t>
   </si>
   <si>
-    <t>/ActionsGIF/技能/牵制咬.gif</t>
-  </si>
-  <si>
     <t>/ActionsGIF/技能/正面后撤步.gif</t>
   </si>
   <si>
@@ -440,13 +437,38 @@
   </si>
   <si>
     <t>二连吐息+冲刺翅膀拍-头翅膀充电</t>
+  </si>
+  <si>
+    <r>
+      <t>/ActionMP4/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="FangSong"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>牵制咬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1.mp4</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
@@ -516,6 +538,13 @@
       <color rgb="FF333333"/>
       <name val="微软雅黑"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="FangSong"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -990,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>10</v>
@@ -998,13 +1027,13 @@
     </row>
     <row r="4" spans="1:4" ht="15">
       <c r="A4" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>10</v>
@@ -1018,7 +1047,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>10</v>
@@ -1032,7 +1061,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
@@ -1040,16 +1069,16 @@
     </row>
     <row r="7" spans="1:4" ht="15">
       <c r="A7" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15">
@@ -1060,7 +1089,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>10</v>
@@ -1074,7 +1103,7 @@
         <v>20</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>10</v>
@@ -1088,7 +1117,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>10</v>
@@ -1102,7 +1131,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>10</v>
@@ -1116,7 +1145,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>10</v>
@@ -1124,13 +1153,13 @@
     </row>
     <row r="13" spans="1:4" ht="15">
       <c r="A13" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>10</v>
@@ -1138,25 +1167,25 @@
     </row>
     <row r="14" spans="1:4" ht="18">
       <c r="A14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="15">
       <c r="A15" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>10</v>
@@ -1164,13 +1193,13 @@
     </row>
     <row r="16" spans="1:4" ht="18">
       <c r="A16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>65</v>
-      </c>
       <c r="C16" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" s="4"/>
     </row>
@@ -1182,7 +1211,7 @@
         <v>31</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>10</v>
@@ -1196,7 +1225,7 @@
         <v>33</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>10</v>
@@ -1204,13 +1233,13 @@
     </row>
     <row r="19" spans="1:4" ht="18">
       <c r="A19" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>10</v>
@@ -1218,13 +1247,13 @@
     </row>
     <row r="20" spans="1:4" ht="18">
       <c r="A20" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>67</v>
-      </c>
       <c r="C20" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>10</v>
@@ -1364,7 +1393,7 @@
         <v>36</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>10</v>

--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAC567A-CA4C-7544-B367-56FF96A457D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5135C8-1B3A-5445-83B0-C58D59269E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6140" yWindow="4100" windowWidth="44820" windowHeight="25320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16200" yWindow="600" windowWidth="14940" windowHeight="25320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -440,14 +440,11 @@
   </si>
   <si>
     <r>
-      <t>/ActionMP4/</t>
-    </r>
-    <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF333333"/>
-        <rFont val="FangSong"/>
-        <family val="3"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>牵制咬</t>
@@ -459,7 +456,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>-1.mp4</t>
+      <t>.mp4</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -543,8 +540,8 @@
     <font>
       <sz val="11"/>
       <color rgb="FF333333"/>
-      <name val="FangSong"/>
-      <family val="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -613,7 +610,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -640,6 +637,7 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1011,14 +1009,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15">
+    <row r="3" spans="1:4" ht="17">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="10" t="s">
         <v>67</v>
       </c>
       <c r="D3" s="4" t="s">

--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED0E2E3-D454-FE49-9965-D332CBCDB154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0743B501-6639-BE43-955E-FF2724FF9C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9340" yWindow="11600" windowWidth="44820" windowHeight="25320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9940" yWindow="6300" windowWidth="44800" windowHeight="25320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
   <si>
     <t>ActionId</t>
   </si>
@@ -88,55 +88,70 @@
     <t>Astaroth_Tail_Thrust</t>
   </si>
   <si>
-    <t>尾刺-尾充能</t>
+    <t>尾刺-尾充电</t>
   </si>
   <si>
     <t>充能尾刺.mp4</t>
   </si>
   <si>
-    <t>尾巴插地放电-未充能.mp4</t>
-  </si>
-  <si>
     <t>Astaroth_Tail_Ground_Spike_Uncharged</t>
   </si>
   <si>
-    <t>尾巴插地放电-未充能</t>
+    <t>尾巴插地放电-未充电</t>
+  </si>
+  <si>
+    <t>尾巴插地放电-尾巴未充电.mp4</t>
   </si>
   <si>
     <t>Astaroth_Head_Slam_Uncharged</t>
   </si>
   <si>
-    <t>头顶二连-未充能</t>
+    <t>头顶二连-未充电</t>
+  </si>
+  <si>
+    <t>头顶二连-未充能.mp4</t>
   </si>
   <si>
     <t>Astaroth_Head_Slam_Charged</t>
   </si>
   <si>
-    <t>头顶二连-头充能</t>
+    <t>头顶二连-头充电</t>
+  </si>
+  <si>
+    <t>头砸二连-充能.mp4</t>
   </si>
   <si>
     <t>Astaroth_Wing_Press_Uncharged</t>
   </si>
   <si>
-    <t>翅膀单次下拍-未充能</t>
+    <t>翅膀单次下拍-未充电</t>
+  </si>
+  <si>
+    <t>单侧翅膀拍地-右-未充能.mp4</t>
   </si>
   <si>
     <t>Astaroth_Wing_Double_Press_Charged</t>
   </si>
   <si>
-    <t>翅膀下拍二连-翅膀充能</t>
+    <t>翅膀下拍二连-翅膀充电</t>
+  </si>
+  <si>
+    <t>翅膀充能二连拍.mp4</t>
   </si>
   <si>
     <t>Astaroth_Dash_Wing_Press_Charged</t>
   </si>
   <si>
-    <t>冲刺翅膀下拍-翅膀充能</t>
+    <t>冲刺翅膀下拍-翅膀充电</t>
+  </si>
+  <si>
+    <t>冲刺翅膀下拍-翅膀充能.mp4</t>
   </si>
   <si>
     <t>Astaroth_Breath_Uncharged</t>
   </si>
   <si>
-    <t>吐息-未充能</t>
+    <t>吐息-未充电</t>
   </si>
   <si>
     <t>电流吐息-未充能.mp4</t>
@@ -145,13 +160,16 @@
     <t>Astaroth_Double_Breath_Charged</t>
   </si>
   <si>
-    <t>二连吐息-头、翅膀充能</t>
+    <t>二连吐息-头、翅膀充电</t>
+  </si>
+  <si>
+    <t>二连吐息-头充电.mp4</t>
   </si>
   <si>
     <t>Astaroth_Head_Double_Swing_Charged</t>
   </si>
   <si>
-    <t>二连甩头-头、翅膀充能</t>
+    <t>二连甩头-头、翅膀充电</t>
   </si>
   <si>
     <t>二连甩头.mp4</t>
@@ -160,16 +178,16 @@
     <t>Astaroth_Overhead_Slam_Charged</t>
   </si>
   <si>
-    <t>斩舰刀-头充能</t>
-  </si>
-  <si>
-    <t>斩舰刀-充能.mp4</t>
+    <t>斩舰刀-头充电</t>
+  </si>
+  <si>
+    <t>斩舰刀-头充能.mp4</t>
   </si>
   <si>
     <t>Astaroth_AllCharged_Roar</t>
   </si>
   <si>
-    <t>全身充能吼叫</t>
+    <t>全身充电吼叫</t>
   </si>
   <si>
     <t>进入完全充电状态.mp4</t>
@@ -187,10 +205,7 @@
     <t>Astaroth_Double_Breath_Combo</t>
   </si>
   <si>
-    <t>二连吐息+冲刺翅膀拍-头翅膀充电</t>
-  </si>
-  <si>
-    <t>二连吐息+冲刺翅膀拍-头翅膀充电.mp4</t>
+    <t>二连吐息+冲刺翅膀拍-头、翅膀充电</t>
   </si>
   <si>
     <t>Astaroth_</t>
@@ -202,8 +217,11 @@
     <t>大招-闪电俯冲</t>
   </si>
   <si>
+    <t>全身放电攻击.mp4</t>
+  </si>
+  <si>
     <r>
-      <t>翅膀充能二连拍</t>
+      <t>二连吐息</t>
     </r>
     <r>
       <rPr>
@@ -211,14 +229,18 @@
         <color rgb="FF111827"/>
         <rFont val="Arial"/>
         <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="FangSong"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>.mp4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>二连吐息</t>
+      <t>冲刺翅膀拍</t>
     </r>
     <r>
       <rPr>
@@ -237,7 +259,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>头充电</t>
+      <t>头翅膀充电</t>
     </r>
     <r>
       <rPr>
@@ -249,210 +271,12 @@
       <t>.mp4</t>
     </r>
   </si>
-  <si>
-    <r>
-      <t>单侧翅膀拍地</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="FangSong"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>右</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="FangSong"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>未充能</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>全身放电攻击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>尾巴插地放电</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="FangSong"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>尾巴未充电</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>冲刺翅膀下拍</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="FangSong"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>翅膀充能</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>头顶二连</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="FangSong"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>未充能</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>头砸二连</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="FangSong"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>充能</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
@@ -481,13 +305,6 @@
       <sz val="9"/>
       <name val="FangSong"/>
       <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111827"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -563,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -580,10 +397,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -924,8 +738,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="2" max="2" width="32.1640625" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1013,7 +827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
@@ -1024,18 +838,18 @@
         <v>23</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>11</v>
@@ -1048,8 +862,8 @@
       <c r="B9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>66</v>
+      <c r="C9" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>11</v>
@@ -1057,13 +871,13 @@
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>67</v>
+        <v>31</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>11</v>
@@ -1071,13 +885,13 @@
     </row>
     <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>62</v>
+        <v>34</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>11</v>
@@ -1085,13 +899,13 @@
     </row>
     <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>11</v>
@@ -1099,13 +913,13 @@
     </row>
     <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>65</v>
+        <v>40</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>11</v>
@@ -1113,13 +927,13 @@
     </row>
     <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>11</v>
@@ -1127,13 +941,13 @@
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>61</v>
+        <v>46</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
@@ -1141,13 +955,13 @@
     </row>
     <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>11</v>
@@ -1155,13 +969,13 @@
     </row>
     <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>11</v>
@@ -1169,13 +983,13 @@
     </row>
     <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>11</v>
@@ -1183,27 +997,27 @@
     </row>
     <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>56</v>
+        <v>61</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>11</v>
@@ -1211,19 +1025,21 @@
     </row>
     <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="7"/>
+      <c r="C21" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
@@ -1237,7 +1053,7 @@
     </row>
     <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>11</v>
@@ -1251,7 +1067,7 @@
     </row>
     <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
@@ -1265,7 +1081,7 @@
     </row>
     <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>11</v>
@@ -1279,7 +1095,7 @@
     </row>
     <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
@@ -1293,7 +1109,7 @@
     </row>
     <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>11</v>
@@ -1307,7 +1123,7 @@
     </row>
     <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
@@ -1321,7 +1137,7 @@
     </row>
     <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>11</v>
@@ -1335,13 +1151,13 @@
     </row>
     <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>11</v>

--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0743B501-6639-BE43-955E-FF2724FF9C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D531F6-AFD3-F942-BC29-6E4384D8724E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9940" yWindow="6300" windowWidth="44800" windowHeight="25320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1280" yWindow="600" windowWidth="44800" windowHeight="23820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="70">
   <si>
     <t>ActionId</t>
   </si>
@@ -271,12 +271,81 @@
       <t>.mp4</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>尾巴插地</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="FangSong"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>尾巴充能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>尾巴插地放电</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>尾巴充电</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Astaroth_Tail_Ground_Spike_Charged</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
@@ -312,6 +381,20 @@
       <color rgb="FF111827"/>
       <name val="FangSong"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -380,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -398,6 +481,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -734,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -855,317 +941,330 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.15">
+      <c r="A9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A11" s="4" t="s">
+      <c r="D11" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A12" s="5" t="s">
+      <c r="D12" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A13" s="4" t="s">
+      <c r="D13" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A14" s="5" t="s">
+      <c r="D14" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A15" s="4" t="s">
+      <c r="D15" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="s">
+      <c r="D16" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A17" s="4" t="s">
+      <c r="D17" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A18" s="5" t="s">
+      <c r="D18" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A19" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A19" s="4" t="s">
+      <c r="D19" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A20" s="5" t="s">
+      <c r="D20" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C21" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A21" s="4" t="s">
+      <c r="D21" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A22" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A22" s="5" t="s">
+      <c r="B22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A23" s="4" t="s">
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A24" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A24" s="5" t="s">
+      <c r="B24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A25" s="4" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A26" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A26" s="5" t="s">
+      <c r="B26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A27" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A27" s="4" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A28" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A28" s="5" t="s">
+      <c r="B28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A29" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A29" s="4" t="s">
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A30" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.15">
-      <c r="A30" s="5" t="s">
+      <c r="B30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.15">
+      <c r="A31" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B31" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D30" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:D31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Code/web-behavior-tree/public/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE3C10B-FA14-704A-B6C5-64BADF503189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91A6B8C-D073-4242-9B48-7F360F6009C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1280" yWindow="600" windowWidth="44800" windowHeight="23820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -169,18 +169,12 @@
     <t>Astaroth_Double_Breath_Charged</t>
   </si>
   <si>
-    <t>二连吐息-头、翅膀充电</t>
-  </si>
-  <si>
     <t>二连吐息-头充电.mp4</t>
   </si>
   <si>
     <t>Astaroth_Head_Double_Swing_Charged</t>
   </si>
   <si>
-    <t>二连甩头-头、翅膀充电</t>
-  </si>
-  <si>
     <t>二连甩头.mp4</t>
   </si>
   <si>
@@ -245,13 +239,77 @@
   </si>
   <si>
     <t>全身放电攻击.mp4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二连甩头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二连吐息</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111827"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头充电</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF1F2937"/>
@@ -293,6 +351,13 @@
       <sz val="11"/>
       <color rgb="FF111827"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -362,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -385,11 +450,25 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF4D4F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -916,95 +995,95 @@
       <c r="A16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="D17" s="5"/>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="D19" s="5"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="D20" s="4"/>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="D22" s="4"/>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>70</v>
       </c>
       <c r="D23" s="5"/>
     </row>
@@ -1052,19 +1131,29 @@
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="D31" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:D31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="A3:A1048576">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>AND(A3&lt;&gt;"",COUNTIF($A:$A,A3)&gt;1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ActionId 重复" error="A列已有相同 ActionId，请使用唯一 ID。" promptTitle="ActionId 唯一性" prompt="ActionId 需要在 A 列保持唯一。" sqref="A3:A1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>OR(A3="",COUNTIF($A:$A,A3)=1)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActionConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ActionConfig'!$A$2:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ActionConfig'!$A$2:$D$33</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1080,8 +1080,26 @@
       </c>
       <c r="D32" s="5" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Astaroth_Check_Bite_Head_Slam_Combo</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>牵制咬+头顶二连Combo</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>牵制咬+头顶二连Combo.mp4</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D32"/>
+  <autoFilter ref="A2:D33"/>
   <conditionalFormatting sqref="A3:A1048576">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(A3&lt;&gt;"",COUNTIF($A:$A,A3)&gt;1)</formula>

--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -1,40 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActionConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ActionConfig'!$A$2:$D$36</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
+      <name val="Arial"/>
+      <color rgb="FF1F2937"/>
       <sz val="11"/>
-      <color rgb="FF1F2937"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="FF374151"/>
       <sz val="10"/>
-      <color rgb="FF374151"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="FF111827"/>
       <sz val="11"/>
-      <color rgb="FF111827"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -104,43 +109,397 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFill="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFill="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFill="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFill="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFill="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFill="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -203,11 +562,7 @@
           <t>牵制咬.mp4</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -225,11 +580,7 @@
           <t>正面后撤步.mp4</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -247,11 +598,7 @@
           <t>前冲咬.mp4</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -269,11 +616,7 @@
           <t>180甩尾.mp4</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -291,11 +634,7 @@
           <t>充能尾刺.mp4</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -313,11 +652,7 @@
           <t>尾巴插地放电-尾巴未充电.mp4</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -335,11 +670,7 @@
           <t>尾巴插地-尾巴充能.mp4</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -357,11 +688,7 @@
           <t>头顶二连-未充能.mp4</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -379,11 +706,7 @@
           <t>头砸二连-充能.mp4</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -401,11 +724,7 @@
           <t>单侧翅膀拍地-右-未充能.mp4</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -423,11 +742,7 @@
           <t>翅膀充能二连拍.mp4</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -445,11 +760,7 @@
           <t>冲刺翅膀下拍-翅膀充能.mp4</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -467,11 +778,7 @@
           <t>电流吐息-未充能.mp4</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -489,11 +796,7 @@
           <t>二连吐息-头充电.mp4</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -511,11 +814,7 @@
           <t>二连甩头.mp4</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -533,11 +832,7 @@
           <t>斩舰刀-头充能.mp4</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -555,11 +850,7 @@
           <t>进入完全充电状态.mp4</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -577,11 +868,7 @@
           <t>小咬甩尾尾刺三连.mp4</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -599,11 +886,7 @@
           <t>二连吐息+冲刺翅膀拍-头翅膀充电.mp4</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -621,11 +904,7 @@
           <t>翅膀二连第一下.mp4</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -643,11 +922,7 @@
           <t>翅膀二连第二下.mp4</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -665,11 +940,7 @@
           <t>全身放电攻击.mp4</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -687,11 +958,7 @@
           <t>后撤步起飞吐息并落地.mp4</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -709,11 +976,7 @@
           <t>牵制咬+头顶二连Combo.mp4</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -731,11 +994,7 @@
           <t>翅膀横刺+飞行龙车.mp4</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -753,11 +1012,7 @@
           <t>翅膀横刺二连.mp4</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -775,11 +1030,7 @@
           <t>进入加速充电状态.mp4</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -797,16 +1048,12 @@
           <t>翅膀横刺+侧飞靠近+落地甩尾.mp4</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Astaroth_Wing_Thrust_Aerial_Breath_Wing_Double_Press_Combo</t>
+          <t>Astaroth_Wing_Thrust_Aerial_Breath_Wing_Repeated_Press_Combo</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -819,14 +1066,100 @@
           <t>翅膀横刺+空中吐息+连续翅膀下拍.mp4</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="D31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Astaroth_Flying_Approach_Aerial_Breath</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>飞行靠近空中吐息</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>飞行靠近空中吐息.mp4</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Astaroth_Side_Fly_Land_Tail_Sweep_Combo</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>侧飞靠近+落地甩尾</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>侧飞靠近+落地甩尾.mp4</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Astaroth_Back_Step_Takeoff_Wing_Repeated_Press_Combo</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>后撤起飞翅膀连续下拍</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>后撤起飞翅膀连续下拍.mp4</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Astaroth_Back_Step_Takeoff_Tail_Thrust</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>后撤步起飞尾刺</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>后撤步起飞尾刺.mp4</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Astaroth_Flying_Approach_Land</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>飞行靠近+落地</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>飞行靠近+落地.mp4</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D31"/>
+  <autoFilter ref="A2:D36"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -6,7 +6,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActionConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ActionConfig'!$A$2:$D$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ActionConfig'!$A$2:$D$37</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1158,8 +1158,26 @@
       </c>
       <c r="D36" s="5" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Astaroth_Aerial_Double_Breath</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>空中二连吐息</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>空中二连吐息.mp4</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D36"/>
+  <autoFilter ref="A2:D37"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/config/Actions.xlsx
+++ b/public/config/Actions.xlsx
@@ -6,7 +6,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActionConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ActionConfig'!$A$2:$D$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ActionConfig'!$A$2:$D$38</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1176,8 +1176,26 @@
       </c>
       <c r="D37" s="5" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Astaroth_Supercharged_Aerial_Breath_Combo</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>超带电空中吐息连段</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>超带电空中吐息连段.mp4</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D37"/>
+  <autoFilter ref="A2:D38"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>